--- a/발주서-웹서비스/backend/templates/백도복숭아_쥬얼리프룻_소싱현황_원본.xlsx
+++ b/발주서-웹서비스/backend/templates/백도복숭아_쥬얼리프룻_소싱현황_원본.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Library/CloudStorage/MYBOX-hcmpolo/개인 폴더/이커머스백업/0.소싱관리/농수산과일 단가 변동/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\공유\공유받은\이커머스백업\0.소싱관리\농수산과일 단가 변동\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26C256D-8F7F-A84A-A9C1-4B9525EDFA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B442AC86-501E-4596-926B-C35BF30AD762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39340" yWindow="600" windowWidth="36000" windowHeight="19500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="쥬얼리프룻" sheetId="1" r:id="rId1"/>
@@ -104,23 +104,13 @@
     <t>경쟁사2</t>
   </si>
   <si>
-    <t>쥬얼리프룻</t>
+    <t>딱딱이 백도 복숭아</t>
+  </si>
+  <si>
+    <t>중과 1kg (5-6과 내외)</t>
   </si>
   <si>
     <t>https://pbfcompany.adminplus.co.kr/partner/?mod=product&amp;actpage=prt.list&amp;searchval=%EC%B9%B4%EB%9D%BC</t>
-  </si>
-  <si>
-    <t>발주마감시간 : 오전 10시 0분까지</t>
-  </si>
-  <si>
-    <t>쿠폰가 500원 다운쿠폰 할인 한 가격으로 설정함</t>
-  </si>
-  <si>
-    <t>딱딱이 백도 복숭아</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>중과 1kg (5-6과 내외)</t>
   </si>
   <si>
     <t>중과 2kg (11-14과 내외)</t>
@@ -136,7 +126,15 @@
   </si>
   <si>
     <t>대과 4kg (12-17과 내외)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>발주마감시간 : 오전 10시 0분까지</t>
+  </si>
+  <si>
+    <t>쿠폰가 500원 다운쿠폰 할인 한 가격으로 설정함</t>
+  </si>
+  <si>
+    <t>쥬얼리프룻</t>
   </si>
 </sst>
 </file>
@@ -1107,36 +1105,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z817"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="4.1640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="5.83203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="27.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="4.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="5.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="5.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="27.28515625" style="1" customWidth="1"/>
     <col min="5" max="5" width="33" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="16" customWidth="1"/>
-    <col min="11" max="11" width="11.5" style="1" customWidth="1"/>
-    <col min="12" max="12" width="6.5" style="2" customWidth="1"/>
-    <col min="13" max="13" width="5.5" style="2" customWidth="1"/>
-    <col min="14" max="14" width="11.5" style="1" customWidth="1"/>
-    <col min="15" max="15" width="0.83203125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="11.5" style="1" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" style="16" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="6.42578125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="5.42578125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="0.85546875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="11.42578125" style="1" hidden="1" customWidth="1"/>
     <col min="17" max="17" width="2" style="1" customWidth="1"/>
-    <col min="18" max="18" width="9.33203125" style="1" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="7.33203125" style="1" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="5.83203125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="1.33203125" style="38" customWidth="1"/>
-    <col min="24" max="24" width="15.33203125" style="15" customWidth="1"/>
+    <col min="18" max="18" width="9.28515625" style="1" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="7.28515625" style="1" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="5.85546875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.42578125" style="38" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="1.28515625" style="38" customWidth="1"/>
+    <col min="24" max="24" width="15.28515625" style="15" customWidth="1"/>
     <col min="25" max="25" width="15" style="13" customWidth="1"/>
-    <col min="26" max="26" width="15.5" style="13" customWidth="1"/>
-    <col min="27" max="27" width="14.5" style="1" customWidth="1"/>
-    <col min="28" max="16384" width="14.5" style="1"/>
+    <col min="26" max="26" width="15.42578125" style="13" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" customWidth="1"/>
+    <col min="29" max="16384" width="14.42578125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1" thickBot="1"/>
@@ -1348,21 +1346,21 @@
         <v>1</v>
       </c>
       <c r="C8" s="67" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D8" s="68"/>
       <c r="E8" s="65" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F8" s="34">
         <v>1</v>
       </c>
       <c r="G8" s="25">
-        <f t="shared" ref="G8:G12" si="0">H8+500</f>
-        <v>12400</v>
+        <f t="shared" ref="G8:G13" si="0">H8+500</f>
+        <v>10300</v>
       </c>
       <c r="H8" s="24">
-        <v>11900</v>
+        <v>9800</v>
       </c>
       <c r="I8" s="63">
         <v>7300</v>
@@ -1379,40 +1377,40 @@
       </c>
       <c r="N8" s="27">
         <f>H8*5%</f>
-        <v>595</v>
+        <v>490</v>
       </c>
       <c r="O8" s="26"/>
       <c r="P8" s="32">
-        <f t="shared" ref="P8:P12" si="1">(G8*K8)+(H8*3.63%)</f>
-        <v>1877.81</v>
+        <f t="shared" ref="P8:P13" si="1">(G8*K8)+(H8*3.63%)</f>
+        <v>1556.72</v>
       </c>
       <c r="Q8" s="32">
-        <f t="shared" ref="Q8:Q12" si="2">((G8+H8)-(I8+L8+M8+N8+P8))*0%</f>
+        <f t="shared" ref="Q8:Q13" si="2">((H8)-(I8+L8+M8+N8+P8))*0%</f>
         <v>0</v>
       </c>
       <c r="R8" s="32">
-        <f t="shared" ref="R8:R12" si="3">H8-I8-L8-M8-N8-P8-Q8</f>
-        <v>2127.19</v>
+        <f t="shared" ref="R8:R13" si="3">H8-I8-L8-M8-N8-P8-Q8</f>
+        <v>453.28</v>
       </c>
       <c r="S8" s="32">
-        <f t="shared" ref="S8:S12" si="4">R8*16%</f>
-        <v>340.35040000000004</v>
+        <f t="shared" ref="S8:S13" si="4">R8*16%</f>
+        <v>72.524799999999999</v>
       </c>
       <c r="T8" s="33">
-        <f t="shared" ref="T8:T12" si="5">G8*1%</f>
-        <v>124</v>
+        <f t="shared" ref="T8:T13" si="5">G8*1%</f>
+        <v>103</v>
       </c>
       <c r="U8" s="41">
-        <f t="shared" ref="U8:U12" si="6">H8-I8-L8-M8-N8-P8-Q8-S8-T8</f>
-        <v>1662.8396</v>
+        <f t="shared" ref="U8:U13" si="6">H8-I8-L8-M8-N8-P8-Q8-S8-T8</f>
+        <v>277.75519999999995</v>
       </c>
       <c r="V8" s="43">
-        <f t="shared" ref="V8:V12" si="7">IF(U8=0,"",U8/G8)</f>
-        <v>0.13409996774193547</v>
+        <f t="shared" ref="V8:V13" si="7">IF(U8=0,"",U8/G8)</f>
+        <v>2.6966524271844657E-2</v>
       </c>
       <c r="W8" s="37"/>
       <c r="X8" s="53" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y8" s="52"/>
       <c r="Z8" s="36"/>
@@ -1423,21 +1421,21 @@
         <v>2</v>
       </c>
       <c r="C9" s="67" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D9" s="68"/>
       <c r="E9" s="65" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F9" s="34">
         <v>1</v>
       </c>
       <c r="G9" s="25">
         <f t="shared" si="0"/>
-        <v>17300</v>
+        <v>15300</v>
       </c>
       <c r="H9" s="24">
-        <v>16800</v>
+        <v>14800</v>
       </c>
       <c r="I9" s="64">
         <v>10000</v>
@@ -1454,12 +1452,12 @@
       </c>
       <c r="N9" s="27">
         <f>H9*5%</f>
-        <v>840</v>
+        <v>740</v>
       </c>
       <c r="O9" s="26"/>
       <c r="P9" s="32">
         <f t="shared" si="1"/>
-        <v>2627.02</v>
+        <v>2321.2200000000003</v>
       </c>
       <c r="Q9" s="32">
         <f t="shared" si="2"/>
@@ -1467,27 +1465,27 @@
       </c>
       <c r="R9" s="32">
         <f t="shared" si="3"/>
-        <v>3332.98</v>
+        <v>1738.7799999999997</v>
       </c>
       <c r="S9" s="32">
         <f t="shared" si="4"/>
-        <v>533.27679999999998</v>
+        <v>278.20479999999998</v>
       </c>
       <c r="T9" s="33">
         <f t="shared" si="5"/>
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="U9" s="41">
         <f t="shared" si="6"/>
-        <v>2626.7031999999999</v>
+        <v>1307.5751999999998</v>
       </c>
       <c r="V9" s="43">
         <f t="shared" si="7"/>
-        <v>0.15183255491329478</v>
+        <v>8.5462431372549011E-2</v>
       </c>
       <c r="W9" s="37"/>
       <c r="X9" s="53" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y9" s="52"/>
       <c r="Z9" s="36"/>
@@ -1498,21 +1496,21 @@
         <v>3</v>
       </c>
       <c r="C10" s="67" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D10" s="68"/>
       <c r="E10" s="65" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F10" s="34">
         <v>1</v>
       </c>
       <c r="G10" s="25">
         <f t="shared" si="0"/>
-        <v>27300</v>
+        <v>23300</v>
       </c>
       <c r="H10" s="24">
-        <v>26800</v>
+        <v>22800</v>
       </c>
       <c r="I10" s="64">
         <v>16000</v>
@@ -1528,13 +1526,13 @@
         <v>0</v>
       </c>
       <c r="N10" s="27">
-        <f t="shared" ref="N10:N12" si="8">H10*3%</f>
-        <v>804</v>
+        <f>H10*3%</f>
+        <v>684</v>
       </c>
       <c r="O10" s="26"/>
       <c r="P10" s="32">
         <f t="shared" si="1"/>
-        <v>4156.0199999999995</v>
+        <v>3544.4199999999996</v>
       </c>
       <c r="Q10" s="32">
         <f t="shared" si="2"/>
@@ -1542,27 +1540,27 @@
       </c>
       <c r="R10" s="32">
         <f t="shared" si="3"/>
-        <v>5839.9800000000005</v>
+        <v>2571.5800000000004</v>
       </c>
       <c r="S10" s="32">
         <f t="shared" si="4"/>
-        <v>934.3968000000001</v>
+        <v>411.45280000000008</v>
       </c>
       <c r="T10" s="33">
         <f t="shared" si="5"/>
-        <v>273</v>
+        <v>233</v>
       </c>
       <c r="U10" s="41">
         <f t="shared" si="6"/>
-        <v>4632.5832</v>
+        <v>1927.1272000000004</v>
       </c>
       <c r="V10" s="43">
         <f t="shared" si="7"/>
-        <v>0.16969169230769232</v>
+        <v>8.2709321888412027E-2</v>
       </c>
       <c r="W10" s="37"/>
       <c r="X10" s="53" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y10" s="52"/>
       <c r="Z10" s="54"/>
@@ -1573,24 +1571,24 @@
         <v>7</v>
       </c>
       <c r="C11" s="67" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D11" s="68"/>
       <c r="E11" s="65" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F11" s="34">
         <v>1</v>
       </c>
       <c r="G11" s="25">
         <f t="shared" si="0"/>
-        <v>15300</v>
+        <v>14300</v>
       </c>
       <c r="H11" s="24">
-        <v>14800</v>
+        <v>13800</v>
       </c>
       <c r="I11" s="64">
-        <v>9800</v>
+        <v>8800</v>
       </c>
       <c r="J11" s="55">
         <v>0</v>
@@ -1603,13 +1601,13 @@
         <v>0</v>
       </c>
       <c r="N11" s="27">
-        <f t="shared" si="8"/>
-        <v>444</v>
+        <f>H11*3%</f>
+        <v>414</v>
       </c>
       <c r="O11" s="26"/>
       <c r="P11" s="58">
         <f t="shared" si="1"/>
-        <v>2321.2200000000003</v>
+        <v>2168.3199999999997</v>
       </c>
       <c r="Q11" s="58">
         <f t="shared" si="2"/>
@@ -1617,28 +1615,28 @@
       </c>
       <c r="R11" s="58">
         <f t="shared" si="3"/>
-        <v>2234.7799999999997</v>
+        <v>2417.6800000000003</v>
       </c>
       <c r="S11" s="58">
         <f t="shared" si="4"/>
-        <v>357.56479999999999</v>
+        <v>386.82880000000006</v>
       </c>
       <c r="T11" s="59">
         <f t="shared" si="5"/>
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="U11" s="60">
         <f t="shared" si="6"/>
-        <v>1724.2151999999996</v>
+        <v>1887.8512000000003</v>
       </c>
       <c r="V11" s="61">
         <f t="shared" si="7"/>
-        <v>0.11269380392156861</v>
+        <v>0.13201756643356646</v>
       </c>
       <c r="W11" s="37"/>
       <c r="X11" s="53"/>
       <c r="Y11" s="52" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z11" s="36"/>
     </row>
@@ -1648,24 +1646,24 @@
         <v>8</v>
       </c>
       <c r="C12" s="67" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D12" s="68"/>
       <c r="E12" s="65" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F12" s="34">
         <v>1</v>
       </c>
       <c r="G12" s="25">
         <f t="shared" si="0"/>
-        <v>20300</v>
+        <v>19300</v>
       </c>
       <c r="H12" s="24">
-        <v>19800</v>
+        <v>18800</v>
       </c>
       <c r="I12" s="64">
-        <v>14300</v>
+        <v>13500</v>
       </c>
       <c r="J12" s="29">
         <v>0</v>
@@ -1678,13 +1676,13 @@
         <v>0</v>
       </c>
       <c r="N12" s="27">
-        <f t="shared" si="8"/>
-        <v>594</v>
+        <f>H12*3%</f>
+        <v>564</v>
       </c>
       <c r="O12" s="26"/>
       <c r="P12" s="32">
         <f t="shared" si="1"/>
-        <v>3085.7200000000003</v>
+        <v>2932.82</v>
       </c>
       <c r="Q12" s="32">
         <f t="shared" si="2"/>
@@ -1692,28 +1690,28 @@
       </c>
       <c r="R12" s="32">
         <f t="shared" si="3"/>
-        <v>1820.2799999999997</v>
+        <v>1803.1799999999998</v>
       </c>
       <c r="S12" s="32">
         <f t="shared" si="4"/>
-        <v>291.24479999999994</v>
+        <v>288.50880000000001</v>
       </c>
       <c r="T12" s="33">
         <f t="shared" si="5"/>
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="U12" s="41">
         <f t="shared" si="6"/>
-        <v>1326.0351999999998</v>
+        <v>1321.6711999999998</v>
       </c>
       <c r="V12" s="43">
         <f t="shared" si="7"/>
-        <v>6.532193103448275E-2</v>
+        <v>6.8480373056994809E-2</v>
       </c>
       <c r="W12" s="37"/>
       <c r="X12" s="53"/>
       <c r="Y12" s="52" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z12" s="36"/>
     </row>
@@ -1723,24 +1721,24 @@
         <v>8</v>
       </c>
       <c r="C13" s="67" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D13" s="68"/>
       <c r="E13" s="66" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F13" s="34">
         <v>1</v>
       </c>
       <c r="G13" s="25">
-        <f t="shared" ref="G13" si="9">H13+500</f>
-        <v>34400</v>
+        <f t="shared" si="0"/>
+        <v>33300</v>
       </c>
       <c r="H13" s="24">
-        <v>33900</v>
+        <v>32800</v>
       </c>
       <c r="I13" s="64">
-        <v>25000</v>
+        <v>24000</v>
       </c>
       <c r="J13" s="29">
         <v>0</v>
@@ -1753,42 +1751,42 @@
         <v>0</v>
       </c>
       <c r="N13" s="27">
-        <f t="shared" ref="N13" si="10">H13*3%</f>
-        <v>1017</v>
+        <f>H13*3%</f>
+        <v>984</v>
       </c>
       <c r="O13" s="26"/>
       <c r="P13" s="32">
-        <f t="shared" ref="P13" si="11">(G13*K13)+(H13*3.63%)</f>
-        <v>5241.6099999999997</v>
+        <f t="shared" si="1"/>
+        <v>5073.42</v>
       </c>
       <c r="Q13" s="32">
-        <f t="shared" ref="Q13" si="12">((G13+H13)-(I13+L13+M13+N13+P13))*0%</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R13" s="32">
-        <f t="shared" ref="R13" si="13">H13-I13-L13-M13-N13-P13-Q13</f>
-        <v>2641.3900000000003</v>
+        <f t="shared" si="3"/>
+        <v>2742.58</v>
       </c>
       <c r="S13" s="32">
-        <f t="shared" ref="S13" si="14">R13*16%</f>
-        <v>422.62240000000008</v>
+        <f t="shared" si="4"/>
+        <v>438.81279999999998</v>
       </c>
       <c r="T13" s="33">
-        <f t="shared" ref="T13" si="15">G13*1%</f>
-        <v>344</v>
+        <f t="shared" si="5"/>
+        <v>333</v>
       </c>
       <c r="U13" s="41">
-        <f t="shared" ref="U13" si="16">H13-I13-L13-M13-N13-P13-Q13-S13-T13</f>
-        <v>1874.7676000000001</v>
+        <f t="shared" si="6"/>
+        <v>1970.7671999999998</v>
       </c>
       <c r="V13" s="43">
-        <f t="shared" ref="V13" si="17">IF(U13=0,"",U13/G13)</f>
-        <v>5.4499058139534887E-2</v>
+        <f t="shared" si="7"/>
+        <v>5.9182198198198192E-2</v>
       </c>
       <c r="W13" s="37"/>
       <c r="X13" s="53"/>
       <c r="Y13" s="52" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z13" s="36"/>
     </row>
@@ -1796,11 +1794,11 @@
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="D14" s="3" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
@@ -1855,7 +1853,7 @@
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
       <c r="D16" s="67" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E16" s="68"/>
       <c r="F16" s="3"/>
@@ -24275,15 +24273,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B2:N5"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C9:D9"/>
     <mergeCell ref="C8:D8"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="B2:N5"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C9:D9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/발주서-웹서비스/backend/templates/백도복숭아_쥬얼리프룻_소싱현황_원본.xlsx
+++ b/발주서-웹서비스/backend/templates/백도복숭아_쥬얼리프룻_소싱현황_원본.xlsx
@@ -1433,13 +1433,13 @@
       </c>
       <c r="C8" s="67" t="inlineStr">
         <is>
-          <t>쥬얼리프룻</t>
+          <t>제주다팜</t>
         </is>
       </c>
       <c r="D8" s="68" t="n"/>
       <c r="E8" s="65" t="inlineStr">
         <is>
-          <t>중과 1kg (5-6과 내외)</t>
+          <t>중과 2kg (11-14과 내외)</t>
         </is>
       </c>
       <c r="F8" s="34" t="n">
@@ -1450,10 +1450,10 @@
         <v/>
       </c>
       <c r="H8" s="92" t="n">
-        <v>9800</v>
+        <v>14800</v>
       </c>
       <c r="I8" s="63" t="n">
-        <v>7300</v>
+        <v>10000</v>
       </c>
       <c r="J8" s="93" t="n">
         <v>0</v>
@@ -1520,7 +1520,7 @@
       <c r="D9" s="68" t="n"/>
       <c r="E9" s="65" t="inlineStr">
         <is>
-          <t>중과 2kg (11-14과 내외)</t>
+          <t>중과 4kg (20-26과 내외)</t>
         </is>
       </c>
       <c r="F9" s="34" t="n">
@@ -1531,10 +1531,10 @@
         <v/>
       </c>
       <c r="H9" s="92" t="n">
-        <v>14800</v>
+        <v>22800</v>
       </c>
       <c r="I9" s="64" t="n">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="J9" s="93" t="n">
         <v>0</v>
@@ -1547,7 +1547,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="95">
-        <f>H9*5%</f>
+        <f>H9*3%</f>
         <v/>
       </c>
       <c r="O9" s="96" t="n"/>
@@ -1601,7 +1601,7 @@
       <c r="D10" s="68" t="n"/>
       <c r="E10" s="65" t="inlineStr">
         <is>
-          <t>중과 4kg (20-26과 내외)</t>
+          <t>대과 2kg (6-8과 내외)</t>
         </is>
       </c>
       <c r="F10" s="34" t="n">
@@ -1612,10 +1612,10 @@
         <v/>
       </c>
       <c r="H10" s="92" t="n">
-        <v>22800</v>
+        <v>18800</v>
       </c>
       <c r="I10" s="64" t="n">
-        <v>16000</v>
+        <v>13500</v>
       </c>
       <c r="J10" s="93" t="n">
         <v>0</v>
@@ -1661,28 +1661,28 @@
         <v/>
       </c>
       <c r="W10" s="101" t="n"/>
-      <c r="X10" s="53" t="inlineStr">
+      <c r="X10" s="53" t="n"/>
+      <c r="Y10" s="52" t="inlineStr">
         <is>
           <t>https://pbfcompany.adminplus.co.kr/partner/?mod=product&amp;actpage=prt.list&amp;searchval=%EC%B9%B4%EB%9D%BC</t>
         </is>
       </c>
-      <c r="Y10" s="52" t="n"/>
       <c r="Z10" s="54" t="n"/>
     </row>
     <row r="11" ht="18" customFormat="1" customHeight="1" s="62" thickBot="1">
       <c r="A11" s="28" t="n"/>
       <c r="B11" s="23" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C11" s="67" t="inlineStr">
         <is>
-          <t>쥬얼리프룻</t>
+          <t>제주다팜</t>
         </is>
       </c>
       <c r="D11" s="68" t="n"/>
       <c r="E11" s="65" t="inlineStr">
         <is>
-          <t>대과 1kg (3-4과 내외)</t>
+          <t>대과 4kg (12-17과 내외)</t>
         </is>
       </c>
       <c r="F11" s="34" t="n">
@@ -1693,10 +1693,10 @@
         <v/>
       </c>
       <c r="H11" s="92" t="n">
-        <v>13800</v>
+        <v>32800</v>
       </c>
       <c r="I11" s="64" t="n">
-        <v>8800</v>
+        <v>24000</v>
       </c>
       <c r="J11" s="102" t="n">
         <v>0</v>
@@ -1752,164 +1752,58 @@
     </row>
     <row r="12" ht="18" customHeight="1" s="83" thickBot="1">
       <c r="A12" s="28" t="n"/>
-      <c r="B12" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="C12" s="67" t="inlineStr">
-        <is>
-          <t>제주다팜</t>
-        </is>
-      </c>
+      <c r="B12" s="23" t="n"/>
+      <c r="C12" s="67" t="n"/>
       <c r="D12" s="68" t="n"/>
-      <c r="E12" s="65" t="inlineStr">
-        <is>
-          <t>대과 2kg (6-8과 내외)</t>
-        </is>
-      </c>
-      <c r="F12" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="91">
-        <f>H12+500</f>
-        <v/>
-      </c>
-      <c r="H12" s="92" t="n">
-        <v>18800</v>
-      </c>
-      <c r="I12" s="64" t="n">
-        <v>13500</v>
-      </c>
-      <c r="J12" s="93" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="94" t="n">
-        <v>0.1166</v>
-      </c>
+      <c r="E12" s="65" t="n"/>
+      <c r="F12" s="34" t="n"/>
+      <c r="G12" s="91" t="n"/>
+      <c r="H12" s="92" t="n"/>
+      <c r="I12" s="64" t="n"/>
+      <c r="J12" s="93" t="n"/>
+      <c r="K12" s="94" t="n"/>
       <c r="L12" s="31" t="n"/>
-      <c r="M12" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="95">
-        <f>H12*3%</f>
-        <v/>
-      </c>
+      <c r="M12" s="31" t="n"/>
+      <c r="N12" s="95" t="n"/>
       <c r="O12" s="96" t="n"/>
-      <c r="P12" s="97">
-        <f>(G12*K12)+(H12*3.63%)</f>
-        <v/>
-      </c>
-      <c r="Q12" s="97">
-        <f>((H12)-(I12+L12+M12+N12+P12))*0%</f>
-        <v/>
-      </c>
-      <c r="R12" s="97">
-        <f>H12-I12-L12-M12-N12-P12-Q12</f>
-        <v/>
-      </c>
-      <c r="S12" s="97">
-        <f>R12*16%</f>
-        <v/>
-      </c>
-      <c r="T12" s="98">
-        <f>G12*1%</f>
-        <v/>
-      </c>
-      <c r="U12" s="99">
-        <f>H12-I12-L12-M12-N12-P12-Q12-S12-T12</f>
-        <v/>
-      </c>
-      <c r="V12" s="100">
-        <f>IF(U12=0,"",U12/G12)</f>
-        <v/>
-      </c>
+      <c r="P12" s="97" t="n"/>
+      <c r="Q12" s="97" t="n"/>
+      <c r="R12" s="97" t="n"/>
+      <c r="S12" s="97" t="n"/>
+      <c r="T12" s="98" t="n"/>
+      <c r="U12" s="99" t="n"/>
+      <c r="V12" s="100" t="n"/>
       <c r="W12" s="101" t="n"/>
       <c r="X12" s="53" t="n"/>
-      <c r="Y12" s="52" t="inlineStr">
-        <is>
-          <t>https://pbfcompany.adminplus.co.kr/partner/?mod=product&amp;actpage=prt.list&amp;searchval=%EC%B9%B4%EB%9D%BC</t>
-        </is>
-      </c>
+      <c r="Y12" s="52" t="n"/>
       <c r="Z12" s="36" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1" s="83" thickBot="1">
       <c r="A13" s="28" t="n"/>
-      <c r="B13" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="C13" s="67" t="inlineStr">
-        <is>
-          <t>제주다팜</t>
-        </is>
-      </c>
+      <c r="B13" s="23" t="n"/>
+      <c r="C13" s="67" t="n"/>
       <c r="D13" s="68" t="n"/>
-      <c r="E13" s="66" t="inlineStr">
-        <is>
-          <t>대과 4kg (12-17과 내외)</t>
-        </is>
-      </c>
-      <c r="F13" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="91">
-        <f>H13+500</f>
-        <v/>
-      </c>
-      <c r="H13" s="92" t="n">
-        <v>32800</v>
-      </c>
-      <c r="I13" s="64" t="n">
-        <v>24000</v>
-      </c>
-      <c r="J13" s="93" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="94" t="n">
-        <v>0.1166</v>
-      </c>
+      <c r="E13" s="66" t="n"/>
+      <c r="F13" s="34" t="n"/>
+      <c r="G13" s="91" t="n"/>
+      <c r="H13" s="92" t="n"/>
+      <c r="I13" s="64" t="n"/>
+      <c r="J13" s="93" t="n"/>
+      <c r="K13" s="94" t="n"/>
       <c r="L13" s="31" t="n"/>
-      <c r="M13" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="95">
-        <f>H13*3%</f>
-        <v/>
-      </c>
+      <c r="M13" s="31" t="n"/>
+      <c r="N13" s="95" t="n"/>
       <c r="O13" s="96" t="n"/>
-      <c r="P13" s="97">
-        <f>(G13*K13)+(H13*3.63%)</f>
-        <v/>
-      </c>
-      <c r="Q13" s="97">
-        <f>((H13)-(I13+L13+M13+N13+P13))*0%</f>
-        <v/>
-      </c>
-      <c r="R13" s="97">
-        <f>H13-I13-L13-M13-N13-P13-Q13</f>
-        <v/>
-      </c>
-      <c r="S13" s="97">
-        <f>R13*16%</f>
-        <v/>
-      </c>
-      <c r="T13" s="98">
-        <f>G13*1%</f>
-        <v/>
-      </c>
-      <c r="U13" s="99">
-        <f>H13-I13-L13-M13-N13-P13-Q13-S13-T13</f>
-        <v/>
-      </c>
-      <c r="V13" s="100">
-        <f>IF(U13=0,"",U13/G13)</f>
-        <v/>
-      </c>
+      <c r="P13" s="97" t="n"/>
+      <c r="Q13" s="97" t="n"/>
+      <c r="R13" s="97" t="n"/>
+      <c r="S13" s="97" t="n"/>
+      <c r="T13" s="98" t="n"/>
+      <c r="U13" s="99" t="n"/>
+      <c r="V13" s="100" t="n"/>
       <c r="W13" s="101" t="n"/>
       <c r="X13" s="53" t="n"/>
-      <c r="Y13" s="52" t="inlineStr">
-        <is>
-          <t>https://pbfcompany.adminplus.co.kr/partner/?mod=product&amp;actpage=prt.list&amp;searchval=%EC%B9%B4%EB%9D%BC</t>
-        </is>
-      </c>
+      <c r="Y13" s="52" t="n"/>
       <c r="Z13" s="36" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1" s="83">
